--- a/Estoque/Estoque 08.2026.xlsx
+++ b/Estoque/Estoque 08.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Estoque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C710587-E998-409C-A95C-2A80C3321A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D85008-3B57-4E13-8104-25FC5B5E59C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8E53B96B-8C82-452A-AAB2-5E3C25B6EC39}"/>
+    <workbookView xWindow="-20520" yWindow="1920" windowWidth="20640" windowHeight="11040" xr2:uid="{8E53B96B-8C82-452A-AAB2-5E3C25B6EC39}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -616,14 +616,14 @@
         <v>6914.6852531990153</v>
       </c>
       <c r="G3" s="3">
-        <v>1101091</v>
+        <v>6908753.7400000002</v>
       </c>
       <c r="H3" s="3">
         <v>1015789.52</v>
       </c>
       <c r="I3" s="3">
         <f>H3/G3</f>
-        <v>0.92253003611872231</v>
+        <v>0.14702934251641164</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -814,6 +814,7 @@
       <c r="J13" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
